--- a/artfynd/A 8966-2022 artfynd.xlsx
+++ b/artfynd/A 8966-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 8966-2022 artfynd.xlsx
+++ b/artfynd/A 8966-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2152,6 +2152,141 @@
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>123324450</v>
+      </c>
+      <c r="B15" t="n">
+        <v>90952</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Korpån, Hls</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>604048</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6854092</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Hudiksvall</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Hög</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>2024_1164</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-07-03</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-07-03</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>på gran</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>David Isaksson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Liam Martin</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 8966-2022 artfynd.xlsx
+++ b/artfynd/A 8966-2022 artfynd.xlsx
@@ -2157,7 +2157,7 @@
         <v>123324450</v>
       </c>
       <c r="B15" t="n">
-        <v>90952</v>
+        <v>90955</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>

--- a/artfynd/A 8966-2022 artfynd.xlsx
+++ b/artfynd/A 8966-2022 artfynd.xlsx
@@ -2157,7 +2157,7 @@
         <v>123324450</v>
       </c>
       <c r="B15" t="n">
-        <v>90955</v>
+        <v>90957</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>

--- a/artfynd/A 8966-2022 artfynd.xlsx
+++ b/artfynd/A 8966-2022 artfynd.xlsx
@@ -2157,7 +2157,7 @@
         <v>123324450</v>
       </c>
       <c r="B15" t="n">
-        <v>90957</v>
+        <v>90963</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>

--- a/artfynd/A 8966-2022 artfynd.xlsx
+++ b/artfynd/A 8966-2022 artfynd.xlsx
@@ -2157,7 +2157,7 @@
         <v>123324450</v>
       </c>
       <c r="B15" t="n">
-        <v>90966</v>
+        <v>90983</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>

--- a/artfynd/A 8966-2022 artfynd.xlsx
+++ b/artfynd/A 8966-2022 artfynd.xlsx
@@ -2157,7 +2157,7 @@
         <v>123324450</v>
       </c>
       <c r="B15" t="n">
-        <v>90983</v>
+        <v>90988</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>

--- a/artfynd/A 8966-2022 artfynd.xlsx
+++ b/artfynd/A 8966-2022 artfynd.xlsx
@@ -2157,7 +2157,7 @@
         <v>123324450</v>
       </c>
       <c r="B15" t="n">
-        <v>90988</v>
+        <v>90990</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
